--- a/pcb/JLCPCB_2layers/design/fab_release/jlcpcb/CPL_JLC-assembly.xlsx
+++ b/pcb/JLCPCB_2layers/design/fab_release/jlcpcb/CPL_JLC-assembly.xlsx
@@ -40,211 +40,211 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">C6</t>
+          <t xml:space="preserve">C3</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24mm</t>
+          <t xml:space="preserve">63.5mm</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">-63mm</t>
+          <t xml:space="preserve">-48.5mm</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bottom</t>
+          <t xml:space="preserve">Top</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">C8</t>
+          <t xml:space="preserve">R51</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">46mm</t>
+          <t xml:space="preserve">31mm</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">-103mm</t>
+          <t xml:space="preserve">-38mm</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bottom</t>
+          <t xml:space="preserve">Top</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">90</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">C10</t>
+          <t xml:space="preserve">J5</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">54mm</t>
+          <t xml:space="preserve">36.75mm</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">-103mm</t>
+          <t xml:space="preserve">-69.1mm</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bottom</t>
+          <t xml:space="preserve">Top</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">180</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">C11</t>
+          <t xml:space="preserve">C31</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">50mm</t>
+          <t xml:space="preserve">44mm</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">-72mm</t>
+          <t xml:space="preserve">-20mm</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bottom</t>
+          <t xml:space="preserve">Top</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">180</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">C12</t>
+          <t xml:space="preserve">D1</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">42mm</t>
+          <t xml:space="preserve">21.43mm</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">-86mm</t>
+          <t xml:space="preserve">-15mm</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bottom</t>
+          <t xml:space="preserve">Top</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">180</t>
+          <t xml:space="preserve">90</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">C14</t>
+          <t xml:space="preserve">C7</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">60mm</t>
+          <t xml:space="preserve">66.5mm</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">-60mm</t>
+          <t xml:space="preserve">-58.5mm</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bottom</t>
+          <t xml:space="preserve">Top</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">180</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">D29</t>
+          <t xml:space="preserve">C18</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">84mm</t>
+          <t xml:space="preserve">76mm</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">-64mm</t>
+          <t xml:space="preserve">-50mm</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bottom</t>
+          <t xml:space="preserve">Top</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">90</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q34</t>
+          <t xml:space="preserve">J1</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">72mm</t>
+          <t xml:space="preserve">90.25mm</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">-66mm</t>
+          <t xml:space="preserve">-114mm</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bottom</t>
+          <t xml:space="preserve">Top</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -256,22 +256,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">R1</t>
+          <t xml:space="preserve">Q30</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">92.5mm</t>
+          <t xml:space="preserve">30mm</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">-48mm</t>
+          <t xml:space="preserve">-43mm</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bottom</t>
+          <t xml:space="preserve">Top</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -283,22 +283,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">R2</t>
+          <t xml:space="preserve">Q17</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">16mm</t>
+          <t xml:space="preserve">50mm</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">-63mm</t>
+          <t xml:space="preserve">-37.5mm</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bottom</t>
+          <t xml:space="preserve">Top</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -310,130 +310,130 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">R3</t>
+          <t xml:space="preserve">L2</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">20mm</t>
+          <t xml:space="preserve">86.5mm</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">-63mm</t>
+          <t xml:space="preserve">-57.5mm</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bottom</t>
+          <t xml:space="preserve">Top</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">180</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">R10</t>
+          <t xml:space="preserve">D25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">76mm</t>
+          <t xml:space="preserve">30mm</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">-104mm</t>
+          <t xml:space="preserve">-33mm</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bottom</t>
+          <t xml:space="preserve">Top</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">180</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">R12</t>
+          <t xml:space="preserve">R79</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">64.5mm</t>
+          <t xml:space="preserve">56mm</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">-108.5mm</t>
+          <t xml:space="preserve">-55mm</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bottom</t>
+          <t xml:space="preserve">Top</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">180</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">R13</t>
+          <t xml:space="preserve">SW1</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">30mm</t>
+          <t xml:space="preserve">44.45mm</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">-23mm</t>
+          <t xml:space="preserve">-30.25mm</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bottom</t>
+          <t xml:space="preserve">Top</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">180</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">R14</t>
+          <t xml:space="preserve">Q28</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">34mm</t>
+          <t xml:space="preserve">25mm</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">-23mm</t>
+          <t xml:space="preserve">-43mm</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bottom</t>
+          <t xml:space="preserve">Top</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -445,265 +445,265 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">R15</t>
+          <t xml:space="preserve">C16</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">70mm</t>
+          <t xml:space="preserve">92.5mm</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t xml:space="preserve">-23mm</t>
+          <t xml:space="preserve">-53.5mm</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bottom</t>
+          <t xml:space="preserve">Top</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">180</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">R16</t>
+          <t xml:space="preserve">D32</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t xml:space="preserve">66mm</t>
+          <t xml:space="preserve">50mm</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve">-23mm</t>
+          <t xml:space="preserve">-20mm</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bottom</t>
+          <t xml:space="preserve">Top</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">180</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">R17</t>
+          <t xml:space="preserve">D28</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t xml:space="preserve">22mm</t>
+          <t xml:space="preserve">79.5mm</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t xml:space="preserve">-26mm</t>
+          <t xml:space="preserve">-46.5mm</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bottom</t>
+          <t xml:space="preserve">Top</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">180</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">R18</t>
+          <t xml:space="preserve">SW5</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t xml:space="preserve">26mm</t>
+          <t xml:space="preserve">6mm</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t xml:space="preserve">-26mm</t>
+          <t xml:space="preserve">-116.4mm</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bottom</t>
+          <t xml:space="preserve">Top</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">180</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">R19</t>
+          <t xml:space="preserve">C5</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t xml:space="preserve">78mm</t>
+          <t xml:space="preserve">71mm</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve">-26mm</t>
+          <t xml:space="preserve">-54mm</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bottom</t>
+          <t xml:space="preserve">Top</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">180</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">R20</t>
+          <t xml:space="preserve">D5</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t xml:space="preserve">74mm</t>
+          <t xml:space="preserve">15mm</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t xml:space="preserve">-26mm</t>
+          <t xml:space="preserve">-44.2mm</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bottom</t>
+          <t xml:space="preserve">Top</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">180</t>
+          <t xml:space="preserve">90</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">R21</t>
+          <t xml:space="preserve">R52</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t xml:space="preserve">22mm</t>
+          <t xml:space="preserve">69mm</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t xml:space="preserve">-39mm</t>
+          <t xml:space="preserve">-38mm</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bottom</t>
+          <t xml:space="preserve">Top</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">180</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">R22</t>
+          <t xml:space="preserve">R53</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t xml:space="preserve">22mm</t>
+          <t xml:space="preserve">35mm</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t xml:space="preserve">-42mm</t>
+          <t xml:space="preserve">-38mm</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bottom</t>
+          <t xml:space="preserve">Top</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">180</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">R23</t>
+          <t xml:space="preserve">C23</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t xml:space="preserve">78mm</t>
+          <t xml:space="preserve">44mm</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t xml:space="preserve">-39mm</t>
+          <t xml:space="preserve">-56mm</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bottom</t>
+          <t xml:space="preserve">Top</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t xml:space="preserve">180</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">R24</t>
+          <t xml:space="preserve">Q16</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t xml:space="preserve">78mm</t>
+          <t xml:space="preserve">40mm</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t xml:space="preserve">-42mm</t>
+          <t xml:space="preserve">-37.5mm</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bottom</t>
+          <t xml:space="preserve">Top</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -715,211 +715,211 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t xml:space="preserve">R56</t>
+          <t xml:space="preserve">D26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t xml:space="preserve">60mm</t>
+          <t xml:space="preserve">70mm</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t xml:space="preserve">-108.5mm</t>
+          <t xml:space="preserve">-33mm</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bottom</t>
+          <t xml:space="preserve">Top</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve">180</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">R57</t>
+          <t xml:space="preserve">D23</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t xml:space="preserve">44mm</t>
+          <t xml:space="preserve">21.43mm</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t xml:space="preserve">-100mm</t>
+          <t xml:space="preserve">-19.6mm</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bottom</t>
+          <t xml:space="preserve">Top</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">180</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t xml:space="preserve">R58</t>
+          <t xml:space="preserve">D6</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t xml:space="preserve">56mm</t>
+          <t xml:space="preserve">85mm</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t xml:space="preserve">-100mm</t>
+          <t xml:space="preserve">-44.2mm</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bottom</t>
+          <t xml:space="preserve">Top</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve">180</t>
+          <t xml:space="preserve">270</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t xml:space="preserve">R67</t>
+          <t xml:space="preserve">R54</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t xml:space="preserve">43mm</t>
+          <t xml:space="preserve">65mm</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t xml:space="preserve">-108mm</t>
+          <t xml:space="preserve">-38mm</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bottom</t>
+          <t xml:space="preserve">Top</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">180</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t xml:space="preserve">R68</t>
+          <t xml:space="preserve">F1</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t xml:space="preserve">47mm</t>
+          <t xml:space="preserve">95.5mm</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t xml:space="preserve">-108mm</t>
+          <t xml:space="preserve">-64.5mm</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bottom</t>
+          <t xml:space="preserve">Top</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">180</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t xml:space="preserve">R69</t>
+          <t xml:space="preserve">R62</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t xml:space="preserve">66mm</t>
+          <t xml:space="preserve">44mm</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t xml:space="preserve">-47mm</t>
+          <t xml:space="preserve">-37.5mm</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bottom</t>
+          <t xml:space="preserve">Top</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">180</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t xml:space="preserve">R70</t>
+          <t xml:space="preserve">D31</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t xml:space="preserve">76mm</t>
+          <t xml:space="preserve">38mm</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t xml:space="preserve">-47mm</t>
+          <t xml:space="preserve">-110mm</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bottom</t>
+          <t xml:space="preserve">Top</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">180</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t xml:space="preserve">R71</t>
+          <t xml:space="preserve">J6</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t xml:space="preserve">80mm</t>
+          <t xml:space="preserve">63.25mm</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t xml:space="preserve">-47mm</t>
+          <t xml:space="preserve">-70mm</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bottom</t>
+          <t xml:space="preserve">Top</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -931,125 +931,125 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t xml:space="preserve">R73</t>
+          <t xml:space="preserve">D4</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t xml:space="preserve">95mm</t>
+          <t xml:space="preserve">82.13mm</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t xml:space="preserve">-54mm</t>
+          <t xml:space="preserve">-27.77mm</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bottom</t>
+          <t xml:space="preserve">Top</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t xml:space="preserve">180</t>
+          <t xml:space="preserve">315</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t xml:space="preserve">R74</t>
+          <t xml:space="preserve">R49</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t xml:space="preserve">95mm</t>
+          <t xml:space="preserve">27mm</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t xml:space="preserve">-58mm</t>
+          <t xml:space="preserve">-38mm</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bottom</t>
+          <t xml:space="preserve">Top</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">180</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t xml:space="preserve">R81</t>
+          <t xml:space="preserve">R9</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t xml:space="preserve">66mm</t>
+          <t xml:space="preserve">44mm</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t xml:space="preserve">-64mm</t>
+          <t xml:space="preserve">-47mm</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bottom</t>
+          <t xml:space="preserve">Top</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t xml:space="preserve">270</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t xml:space="preserve">U6</t>
+          <t xml:space="preserve">C9</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t xml:space="preserve">61.5mm</t>
+          <t xml:space="preserve">40mm</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t xml:space="preserve">-112mm</t>
+          <t xml:space="preserve">-60mm</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bottom</t>
+          <t xml:space="preserve">Top</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t xml:space="preserve">180</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t xml:space="preserve">BZ1</t>
+          <t xml:space="preserve">L1</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t xml:space="preserve">76mm</t>
+          <t xml:space="preserve">66mm</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t xml:space="preserve">-62mm</t>
+          <t xml:space="preserve">-53.5mm</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1066,17 +1066,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t xml:space="preserve">C1</t>
+          <t xml:space="preserve">SW2</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t xml:space="preserve">32mm</t>
+          <t xml:space="preserve">53.25mm</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t xml:space="preserve">-54mm</t>
+          <t xml:space="preserve">-30.25mm</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1093,17 +1093,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t xml:space="preserve">C2</t>
+          <t xml:space="preserve">D30</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t xml:space="preserve">37mm</t>
+          <t xml:space="preserve">26mm</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t xml:space="preserve">-54mm</t>
+          <t xml:space="preserve">-110mm</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1120,17 +1120,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t xml:space="preserve">C3</t>
+          <t xml:space="preserve">Q31</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t xml:space="preserve">63.5mm</t>
+          <t xml:space="preserve">70mm</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t xml:space="preserve">-48.5mm</t>
+          <t xml:space="preserve">-43mm</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1140,24 +1140,24 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">180</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t xml:space="preserve">C4</t>
+          <t xml:space="preserve">Q6</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t xml:space="preserve">55mm</t>
+          <t xml:space="preserve">15mm</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t xml:space="preserve">-49mm</t>
+          <t xml:space="preserve">-36.6mm</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1167,24 +1167,24 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">90</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t xml:space="preserve">C5</t>
+          <t xml:space="preserve">Q4</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t xml:space="preserve">71mm</t>
+          <t xml:space="preserve">12.5mm</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t xml:space="preserve">-54mm</t>
+          <t xml:space="preserve">-22.4mm</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1194,24 +1194,24 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">45</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t xml:space="preserve">C7</t>
+          <t xml:space="preserve">R7</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t xml:space="preserve">66.5mm</t>
+          <t xml:space="preserve">25mm</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t xml:space="preserve">-58.5mm</t>
+          <t xml:space="preserve">-50mm</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1228,17 +1228,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t xml:space="preserve">C9</t>
+          <t xml:space="preserve">Q5</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t xml:space="preserve">40mm</t>
+          <t xml:space="preserve">87.5mm</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t xml:space="preserve">-60mm</t>
+          <t xml:space="preserve">-22.4mm</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1248,24 +1248,24 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">315</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t xml:space="preserve">C15</t>
+          <t xml:space="preserve">U3</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t xml:space="preserve">85mm</t>
+          <t xml:space="preserve">50mm</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t xml:space="preserve">-50mm</t>
+          <t xml:space="preserve">-106.7mm</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1275,24 +1275,24 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">180</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t xml:space="preserve">C16</t>
+          <t xml:space="preserve">D2</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t xml:space="preserve">92.5mm</t>
+          <t xml:space="preserve">78.57mm</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t xml:space="preserve">-53.5mm</t>
+          <t xml:space="preserve">-15mm</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1302,24 +1302,24 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">90</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t xml:space="preserve">C17</t>
+          <t xml:space="preserve">BZ1</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t xml:space="preserve">92.5mm</t>
+          <t xml:space="preserve">76mm</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t xml:space="preserve">-58.5mm</t>
+          <t xml:space="preserve">-62mm</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -1336,17 +1336,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t xml:space="preserve">C18</t>
+          <t xml:space="preserve">C30</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t xml:space="preserve">76mm</t>
+          <t xml:space="preserve">12.5mm</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t xml:space="preserve">-50mm</t>
+          <t xml:space="preserve">-57.5mm</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -1356,24 +1356,24 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">180</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t xml:space="preserve">C20</t>
+          <t xml:space="preserve">Q33</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t xml:space="preserve">44mm</t>
+          <t xml:space="preserve">65mm</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t xml:space="preserve">-63mm</t>
+          <t xml:space="preserve">-43mm</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -1383,24 +1383,24 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">180</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t xml:space="preserve">C23</t>
+          <t xml:space="preserve">J7</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t xml:space="preserve">44mm</t>
+          <t xml:space="preserve">70mm</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t xml:space="preserve">-56mm</t>
+          <t xml:space="preserve">-115.675mm</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -1417,17 +1417,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t xml:space="preserve">C24</t>
+          <t xml:space="preserve">R83</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t xml:space="preserve">44mm</t>
+          <t xml:space="preserve">38mm</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t xml:space="preserve">-59.5mm</t>
+          <t xml:space="preserve">-106mm</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -1444,17 +1444,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t xml:space="preserve">C30</t>
+          <t xml:space="preserve">D33</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t xml:space="preserve">12.5mm</t>
+          <t xml:space="preserve">32mm</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t xml:space="preserve">-57.5mm</t>
+          <t xml:space="preserve">-110mm</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -1471,17 +1471,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t xml:space="preserve">C31</t>
+          <t xml:space="preserve">Q32</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t xml:space="preserve">44mm</t>
+          <t xml:space="preserve">35mm</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t xml:space="preserve">-20mm</t>
+          <t xml:space="preserve">-43mm</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -1491,24 +1491,24 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">180</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t xml:space="preserve">D1</t>
+          <t xml:space="preserve">Q1</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t xml:space="preserve">21.43mm</t>
+          <t xml:space="preserve">92.5mm</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t xml:space="preserve">-16.27mm</t>
+          <t xml:space="preserve">-48mm</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -1518,24 +1518,24 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t xml:space="preserve">90</t>
+          <t xml:space="preserve">180</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t xml:space="preserve">D2</t>
+          <t xml:space="preserve">C20</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t xml:space="preserve">78.57mm</t>
+          <t xml:space="preserve">44mm</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t xml:space="preserve">-16.27mm</t>
+          <t xml:space="preserve">-63mm</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -1545,24 +1545,24 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t xml:space="preserve">90</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t xml:space="preserve">D3</t>
+          <t xml:space="preserve">R65</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t xml:space="preserve">16.972mm</t>
+          <t xml:space="preserve">44mm</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t xml:space="preserve">-28.668mm</t>
+          <t xml:space="preserve">-52mm</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -1572,24 +1572,24 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t xml:space="preserve">45</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t xml:space="preserve">D4</t>
+          <t xml:space="preserve">R78</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t xml:space="preserve">81.232mm</t>
+          <t xml:space="preserve">56mm</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t xml:space="preserve">-26.872mm</t>
+          <t xml:space="preserve">-64mm</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -1599,24 +1599,24 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t xml:space="preserve">315</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t xml:space="preserve">D5</t>
+          <t xml:space="preserve">R77</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t xml:space="preserve">15mm</t>
+          <t xml:space="preserve">56mm</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t xml:space="preserve">-45.47mm</t>
+          <t xml:space="preserve">-61mm</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -1626,24 +1626,24 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t xml:space="preserve">90</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t xml:space="preserve">D6</t>
+          <t xml:space="preserve">C4</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t xml:space="preserve">85mm</t>
+          <t xml:space="preserve">55mm</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t xml:space="preserve">-42.93mm</t>
+          <t xml:space="preserve">-49mm</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -1653,24 +1653,24 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t xml:space="preserve">270</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t xml:space="preserve">D23</t>
+          <t xml:space="preserve">SW6</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t xml:space="preserve">21.43mm</t>
+          <t xml:space="preserve">15.5mm</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t xml:space="preserve">-19.6mm</t>
+          <t xml:space="preserve">-116.4mm</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -1687,17 +1687,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t xml:space="preserve">D24</t>
+          <t xml:space="preserve">Q7</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t xml:space="preserve">78.57mm</t>
+          <t xml:space="preserve">85mm</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t xml:space="preserve">-19.6mm</t>
+          <t xml:space="preserve">-36.6mm</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -1707,24 +1707,24 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">270</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t xml:space="preserve">D25</t>
+          <t xml:space="preserve">R11</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t xml:space="preserve">30mm</t>
+          <t xml:space="preserve">34mm</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t xml:space="preserve">-33mm</t>
+          <t xml:space="preserve">-60mm</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -1741,17 +1741,17 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t xml:space="preserve">D26</t>
+          <t xml:space="preserve">SW3</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t xml:space="preserve">70mm</t>
+          <t xml:space="preserve">63.25mm</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t xml:space="preserve">-33mm</t>
+          <t xml:space="preserve">-30.25mm</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -1768,17 +1768,17 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t xml:space="preserve">D27</t>
+          <t xml:space="preserve">R82</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t xml:space="preserve">20.5mm</t>
+          <t xml:space="preserve">26mm</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t xml:space="preserve">-46.5mm</t>
+          <t xml:space="preserve">-106mm</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -1795,17 +1795,17 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t xml:space="preserve">D28</t>
+          <t xml:space="preserve">C24</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t xml:space="preserve">79.5mm</t>
+          <t xml:space="preserve">44mm</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t xml:space="preserve">-46.5mm</t>
+          <t xml:space="preserve">-59.5mm</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -1822,17 +1822,17 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t xml:space="preserve">D30</t>
+          <t xml:space="preserve">Q18</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t xml:space="preserve">26mm</t>
+          <t xml:space="preserve">40mm</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t xml:space="preserve">-110mm</t>
+          <t xml:space="preserve">-42mm</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -1842,24 +1842,24 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">180</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t xml:space="preserve">D31</t>
+          <t xml:space="preserve">R63</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t xml:space="preserve">38mm</t>
+          <t xml:space="preserve">54mm</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t xml:space="preserve">-110mm</t>
+          <t xml:space="preserve">-37.5mm</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -1876,17 +1876,17 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t xml:space="preserve">D32</t>
+          <t xml:space="preserve">R50</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t xml:space="preserve">50mm</t>
+          <t xml:space="preserve">73mm</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t xml:space="preserve">-20mm</t>
+          <t xml:space="preserve">-38mm</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -1903,17 +1903,17 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t xml:space="preserve">D33</t>
+          <t xml:space="preserve">R55</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t xml:space="preserve">32mm</t>
+          <t xml:space="preserve">58mm</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t xml:space="preserve">-110mm</t>
+          <t xml:space="preserve">-74mm</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -1930,17 +1930,17 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t xml:space="preserve">F1</t>
+          <t xml:space="preserve">Q2</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t xml:space="preserve">95.5mm</t>
+          <t xml:space="preserve">30.95mm</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t xml:space="preserve">-64.5mm</t>
+          <t xml:space="preserve">-15mm</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -1950,24 +1950,24 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">90</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t xml:space="preserve">J1</t>
+          <t xml:space="preserve">C15</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t xml:space="preserve">89mm</t>
+          <t xml:space="preserve">85mm</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t xml:space="preserve">-114mm</t>
+          <t xml:space="preserve">-50mm</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -1984,17 +1984,17 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t xml:space="preserve">J5</t>
+          <t xml:space="preserve">R64</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t xml:space="preserve">33mm</t>
+          <t xml:space="preserve">44mm</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t xml:space="preserve">-69.1mm</t>
+          <t xml:space="preserve">-42mm</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -2011,17 +2011,17 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t xml:space="preserve">J6</t>
+          <t xml:space="preserve">Q3</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t xml:space="preserve">67mm</t>
+          <t xml:space="preserve">69.05mm</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t xml:space="preserve">-70mm</t>
+          <t xml:space="preserve">-15mm</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -2031,24 +2031,24 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t xml:space="preserve">180</t>
+          <t xml:space="preserve">90</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t xml:space="preserve">J7</t>
+          <t xml:space="preserve">C17</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t xml:space="preserve">70mm</t>
+          <t xml:space="preserve">92.5mm</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t xml:space="preserve">-115.675mm</t>
+          <t xml:space="preserve">-58.5mm</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -2065,17 +2065,17 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t xml:space="preserve">J10</t>
+          <t xml:space="preserve">SW4</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t xml:space="preserve">85.68mm</t>
+          <t xml:space="preserve">67.25mm</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t xml:space="preserve">-104.8mm</t>
+          <t xml:space="preserve">-104.25mm</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -2092,17 +2092,17 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t xml:space="preserve">L1</t>
+          <t xml:space="preserve">C1</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t xml:space="preserve">66mm</t>
+          <t xml:space="preserve">32mm</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t xml:space="preserve">-53.5mm</t>
+          <t xml:space="preserve">-54mm</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -2119,17 +2119,17 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t xml:space="preserve">L2</t>
+          <t xml:space="preserve">U7</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t xml:space="preserve">86.5mm</t>
+          <t xml:space="preserve">81mm</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t xml:space="preserve">-57.5mm</t>
+          <t xml:space="preserve">-54mm</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -2139,24 +2139,24 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">180</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q1</t>
+          <t xml:space="preserve">R6</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t xml:space="preserve">92.5mm</t>
+          <t xml:space="preserve">21mm</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t xml:space="preserve">-48mm</t>
+          <t xml:space="preserve">-50mm</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -2173,17 +2173,17 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q2</t>
+          <t xml:space="preserve">Q29</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t xml:space="preserve">30.95mm</t>
+          <t xml:space="preserve">75mm</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t xml:space="preserve">-16.27mm</t>
+          <t xml:space="preserve">-43mm</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -2193,24 +2193,24 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t xml:space="preserve">90</t>
+          <t xml:space="preserve">180</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q3</t>
+          <t xml:space="preserve">D3</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t xml:space="preserve">69.05mm</t>
+          <t xml:space="preserve">17.87mm</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t xml:space="preserve">-16.27mm</t>
+          <t xml:space="preserve">-27.77mm</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -2220,24 +2220,24 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t xml:space="preserve">90</t>
+          <t xml:space="preserve">45</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q4</t>
+          <t xml:space="preserve">R84</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t xml:space="preserve">11.602mm</t>
+          <t xml:space="preserve">32mm</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t xml:space="preserve">-23.298mm</t>
+          <t xml:space="preserve">-106mm</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -2247,24 +2247,24 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t xml:space="preserve">45</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q5</t>
+          <t xml:space="preserve">D24</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t xml:space="preserve">86.602mm</t>
+          <t xml:space="preserve">78.57mm</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t xml:space="preserve">-21.502mm</t>
+          <t xml:space="preserve">-19.6mm</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -2274,24 +2274,24 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t xml:space="preserve">315</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q6</t>
+          <t xml:space="preserve">R8</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t xml:space="preserve">15mm</t>
+          <t xml:space="preserve">40mm</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t xml:space="preserve">-37.87mm</t>
+          <t xml:space="preserve">-47mm</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -2301,24 +2301,24 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t xml:space="preserve">90</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q7</t>
+          <t xml:space="preserve">C2</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t xml:space="preserve">85mm</t>
+          <t xml:space="preserve">37mm</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t xml:space="preserve">-35.33mm</t>
+          <t xml:space="preserve">-54mm</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -2328,24 +2328,24 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t xml:space="preserve">270</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q16</t>
+          <t xml:space="preserve">J10</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t xml:space="preserve">40mm</t>
+          <t xml:space="preserve">89.28mm</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t xml:space="preserve">-37.5mm</t>
+          <t xml:space="preserve">-104.8mm</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -2362,17 +2362,17 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q17</t>
+          <t xml:space="preserve">U1</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t xml:space="preserve">50mm</t>
+          <t xml:space="preserve">61mm</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t xml:space="preserve">-37.5mm</t>
+          <t xml:space="preserve">-54mm</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -2382,24 +2382,24 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">180</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q18</t>
+          <t xml:space="preserve">R80</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t xml:space="preserve">40mm</t>
+          <t xml:space="preserve">56mm</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t xml:space="preserve">-42mm</t>
+          <t xml:space="preserve">-58mm</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -2416,17 +2416,17 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q28</t>
+          <t xml:space="preserve">D27</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t xml:space="preserve">25mm</t>
+          <t xml:space="preserve">20.5mm</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t xml:space="preserve">-43mm</t>
+          <t xml:space="preserve">-46.5mm</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -2443,22 +2443,22 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q29</t>
+          <t xml:space="preserve">R10</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t xml:space="preserve">75mm</t>
+          <t xml:space="preserve">76mm</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t xml:space="preserve">-43mm</t>
+          <t xml:space="preserve">-104mm</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Top</t>
+          <t xml:space="preserve">Bottom</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -2470,22 +2470,22 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q30</t>
+          <t xml:space="preserve">R14</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t xml:space="preserve">30mm</t>
+          <t xml:space="preserve">34mm</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t xml:space="preserve">-43mm</t>
+          <t xml:space="preserve">-23mm</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Top</t>
+          <t xml:space="preserve">Bottom</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -2497,22 +2497,22 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q31</t>
+          <t xml:space="preserve">R19</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t xml:space="preserve">70mm</t>
+          <t xml:space="preserve">78mm</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t xml:space="preserve">-43mm</t>
+          <t xml:space="preserve">-26mm</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Top</t>
+          <t xml:space="preserve">Bottom</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -2524,22 +2524,22 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q32</t>
+          <t xml:space="preserve">C6</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t xml:space="preserve">35mm</t>
+          <t xml:space="preserve">24mm</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t xml:space="preserve">-43mm</t>
+          <t xml:space="preserve">-63mm</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Top</t>
+          <t xml:space="preserve">Bottom</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -2551,22 +2551,22 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q33</t>
+          <t xml:space="preserve">R16</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t xml:space="preserve">65mm</t>
+          <t xml:space="preserve">66mm</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t xml:space="preserve">-43mm</t>
+          <t xml:space="preserve">-23mm</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Top</t>
+          <t xml:space="preserve">Bottom</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -2578,22 +2578,22 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t xml:space="preserve">R6</t>
+          <t xml:space="preserve">R3</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t xml:space="preserve">21mm</t>
+          <t xml:space="preserve">20mm</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t xml:space="preserve">-50mm</t>
+          <t xml:space="preserve">-63mm</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Top</t>
+          <t xml:space="preserve">Bottom</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -2605,22 +2605,22 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t xml:space="preserve">R7</t>
+          <t xml:space="preserve">U8</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t xml:space="preserve">25mm</t>
+          <t xml:space="preserve">50mm</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t xml:space="preserve">-50mm</t>
+          <t xml:space="preserve">-59mm</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Top</t>
+          <t xml:space="preserve">Bottom</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -2632,22 +2632,22 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t xml:space="preserve">R8</t>
+          <t xml:space="preserve">R13</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t xml:space="preserve">40mm</t>
+          <t xml:space="preserve">30mm</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t xml:space="preserve">-47mm</t>
+          <t xml:space="preserve">-23mm</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Top</t>
+          <t xml:space="preserve">Bottom</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -2659,22 +2659,22 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t xml:space="preserve">R9</t>
+          <t xml:space="preserve">R58</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t xml:space="preserve">44mm</t>
+          <t xml:space="preserve">56mm</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t xml:space="preserve">-47mm</t>
+          <t xml:space="preserve">-100mm</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Top</t>
+          <t xml:space="preserve">Bottom</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -2686,22 +2686,22 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t xml:space="preserve">R11</t>
+          <t xml:space="preserve">R73</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t xml:space="preserve">34mm</t>
+          <t xml:space="preserve">95mm</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t xml:space="preserve">-60mm</t>
+          <t xml:space="preserve">-54mm</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Top</t>
+          <t xml:space="preserve">Bottom</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -2713,22 +2713,22 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t xml:space="preserve">R49</t>
+          <t xml:space="preserve">R17</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t xml:space="preserve">27mm</t>
+          <t xml:space="preserve">22mm</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t xml:space="preserve">-38mm</t>
+          <t xml:space="preserve">-26mm</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Top</t>
+          <t xml:space="preserve">Bottom</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -2740,22 +2740,22 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t xml:space="preserve">R50</t>
+          <t xml:space="preserve">C12</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t xml:space="preserve">73mm</t>
+          <t xml:space="preserve">42mm</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t xml:space="preserve">-38mm</t>
+          <t xml:space="preserve">-86mm</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Top</t>
+          <t xml:space="preserve">Bottom</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -2767,22 +2767,22 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t xml:space="preserve">R51</t>
+          <t xml:space="preserve">R15</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t xml:space="preserve">31mm</t>
+          <t xml:space="preserve">70mm</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t xml:space="preserve">-38mm</t>
+          <t xml:space="preserve">-23mm</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Top</t>
+          <t xml:space="preserve">Bottom</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -2794,76 +2794,76 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t xml:space="preserve">R52</t>
+          <t xml:space="preserve">U2</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t xml:space="preserve">69mm</t>
+          <t xml:space="preserve">50mm</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t xml:space="preserve">-38mm</t>
+          <t xml:space="preserve">-72mm</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Top</t>
+          <t xml:space="preserve">Bottom</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">270</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t xml:space="preserve">R53</t>
+          <t xml:space="preserve">U6</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t xml:space="preserve">35mm</t>
+          <t xml:space="preserve">61.5mm</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t xml:space="preserve">-38mm</t>
+          <t xml:space="preserve">-112mm</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Top</t>
+          <t xml:space="preserve">Bottom</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">180</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t xml:space="preserve">R54</t>
+          <t xml:space="preserve">R1</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t xml:space="preserve">65mm</t>
+          <t xml:space="preserve">92.5mm</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t xml:space="preserve">-38mm</t>
+          <t xml:space="preserve">-48mm</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Top</t>
+          <t xml:space="preserve">Bottom</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -2875,22 +2875,22 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t xml:space="preserve">R55</t>
+          <t xml:space="preserve">R24</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t xml:space="preserve">58mm</t>
+          <t xml:space="preserve">78mm</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t xml:space="preserve">-74mm</t>
+          <t xml:space="preserve">-42mm</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Top</t>
+          <t xml:space="preserve">Bottom</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -2902,22 +2902,22 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t xml:space="preserve">R62</t>
+          <t xml:space="preserve">C14</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t xml:space="preserve">44mm</t>
+          <t xml:space="preserve">60mm</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t xml:space="preserve">-37.5mm</t>
+          <t xml:space="preserve">-60mm</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Top</t>
+          <t xml:space="preserve">Bottom</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -2929,22 +2929,22 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t xml:space="preserve">R63</t>
+          <t xml:space="preserve">R20</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t xml:space="preserve">54mm</t>
+          <t xml:space="preserve">74mm</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t xml:space="preserve">-37.5mm</t>
+          <t xml:space="preserve">-26mm</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Top</t>
+          <t xml:space="preserve">Bottom</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -2956,22 +2956,22 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t xml:space="preserve">R64</t>
+          <t xml:space="preserve">R70</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t xml:space="preserve">44mm</t>
+          <t xml:space="preserve">76mm</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t xml:space="preserve">-42mm</t>
+          <t xml:space="preserve">-47mm</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Top</t>
+          <t xml:space="preserve">Bottom</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -2983,22 +2983,22 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t xml:space="preserve">R65</t>
+          <t xml:space="preserve">Q34</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t xml:space="preserve">44mm</t>
+          <t xml:space="preserve">72mm</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t xml:space="preserve">-52mm</t>
+          <t xml:space="preserve">-66mm</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Top</t>
+          <t xml:space="preserve">Bottom</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -3010,22 +3010,22 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t xml:space="preserve">R77</t>
+          <t xml:space="preserve">R21</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t xml:space="preserve">56mm</t>
+          <t xml:space="preserve">22mm</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t xml:space="preserve">-61mm</t>
+          <t xml:space="preserve">-39mm</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Top</t>
+          <t xml:space="preserve">Bottom</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -3037,22 +3037,22 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t xml:space="preserve">R78</t>
+          <t xml:space="preserve">R71</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t xml:space="preserve">56mm</t>
+          <t xml:space="preserve">80mm</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t xml:space="preserve">-64mm</t>
+          <t xml:space="preserve">-47mm</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Top</t>
+          <t xml:space="preserve">Bottom</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -3064,22 +3064,22 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t xml:space="preserve">R79</t>
+          <t xml:space="preserve">R56</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t xml:space="preserve">56mm</t>
+          <t xml:space="preserve">60mm</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t xml:space="preserve">-55mm</t>
+          <t xml:space="preserve">-108.5mm</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Top</t>
+          <t xml:space="preserve">Bottom</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -3091,22 +3091,22 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t xml:space="preserve">R80</t>
+          <t xml:space="preserve">C11</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t xml:space="preserve">56mm</t>
+          <t xml:space="preserve">50mm</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t xml:space="preserve">-58mm</t>
+          <t xml:space="preserve">-81.5mm</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Top</t>
+          <t xml:space="preserve">Bottom</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -3118,22 +3118,22 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t xml:space="preserve">R82</t>
+          <t xml:space="preserve">R22</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t xml:space="preserve">26mm</t>
+          <t xml:space="preserve">22mm</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t xml:space="preserve">-106mm</t>
+          <t xml:space="preserve">-42mm</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Top</t>
+          <t xml:space="preserve">Bottom</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -3145,76 +3145,76 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t xml:space="preserve">R83</t>
+          <t xml:space="preserve">C8</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t xml:space="preserve">38mm</t>
+          <t xml:space="preserve">46mm</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t xml:space="preserve">-106mm</t>
+          <t xml:space="preserve">-103mm</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Top</t>
+          <t xml:space="preserve">Bottom</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">90</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t xml:space="preserve">R84</t>
+          <t xml:space="preserve">R81</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t xml:space="preserve">32mm</t>
+          <t xml:space="preserve">66mm</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t xml:space="preserve">-106mm</t>
+          <t xml:space="preserve">-64mm</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Top</t>
+          <t xml:space="preserve">Bottom</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">270</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t xml:space="preserve">SW1</t>
+          <t xml:space="preserve">R2</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t xml:space="preserve">40mm</t>
+          <t xml:space="preserve">16mm</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t xml:space="preserve">-28mm</t>
+          <t xml:space="preserve">-63mm</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Top</t>
+          <t xml:space="preserve">Bottom</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -3226,22 +3226,22 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t xml:space="preserve">SW2</t>
+          <t xml:space="preserve">R23</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t xml:space="preserve">64mm</t>
+          <t xml:space="preserve">78mm</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t xml:space="preserve">-102mm</t>
+          <t xml:space="preserve">-39mm</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Top</t>
+          <t xml:space="preserve">Bottom</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -3253,22 +3253,22 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t xml:space="preserve">SW3</t>
+          <t xml:space="preserve">R57</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t xml:space="preserve">50mm</t>
+          <t xml:space="preserve">44mm</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t xml:space="preserve">-28mm</t>
+          <t xml:space="preserve">-100mm</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Top</t>
+          <t xml:space="preserve">Bottom</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -3280,22 +3280,22 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t xml:space="preserve">SW4</t>
+          <t xml:space="preserve">R69</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t xml:space="preserve">60mm</t>
+          <t xml:space="preserve">66mm</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t xml:space="preserve">-28mm</t>
+          <t xml:space="preserve">-47mm</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Top</t>
+          <t xml:space="preserve">Bottom</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -3307,22 +3307,22 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t xml:space="preserve">SW5</t>
+          <t xml:space="preserve">R18</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t xml:space="preserve">6mm</t>
+          <t xml:space="preserve">26mm</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t xml:space="preserve">-116.4mm</t>
+          <t xml:space="preserve">-26mm</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Top</t>
+          <t xml:space="preserve">Bottom</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -3334,22 +3334,22 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t xml:space="preserve">SW6</t>
+          <t xml:space="preserve">C10</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t xml:space="preserve">15.5mm</t>
+          <t xml:space="preserve">54mm</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t xml:space="preserve">-116.4mm</t>
+          <t xml:space="preserve">-103mm</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Top</t>
+          <t xml:space="preserve">Bottom</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -3361,22 +3361,22 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t xml:space="preserve">U1</t>
+          <t xml:space="preserve">R74</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t xml:space="preserve">61mm</t>
+          <t xml:space="preserve">95mm</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t xml:space="preserve">-54mm</t>
+          <t xml:space="preserve">-58mm</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Top</t>
+          <t xml:space="preserve">Bottom</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -3388,76 +3388,76 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t xml:space="preserve">U2</t>
+          <t xml:space="preserve">D29</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t xml:space="preserve">50mm</t>
+          <t xml:space="preserve">84mm</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t xml:space="preserve">-72mm</t>
+          <t xml:space="preserve">-64mm</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Top</t>
+          <t xml:space="preserve">Bottom</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">90</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t xml:space="preserve">U3</t>
+          <t xml:space="preserve">R67</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t xml:space="preserve">50mm</t>
+          <t xml:space="preserve">43mm</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t xml:space="preserve">-106.7mm</t>
+          <t xml:space="preserve">-108mm</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Top</t>
+          <t xml:space="preserve">Bottom</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t xml:space="preserve">180</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t xml:space="preserve">U7</t>
+          <t xml:space="preserve">R12</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t xml:space="preserve">81mm</t>
+          <t xml:space="preserve">64.5mm</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t xml:space="preserve">-54mm</t>
+          <t xml:space="preserve">-108.5mm</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Top</t>
+          <t xml:space="preserve">Bottom</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -3469,22 +3469,22 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t xml:space="preserve">U8</t>
+          <t xml:space="preserve">R68</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t xml:space="preserve">50mm</t>
+          <t xml:space="preserve">47mm</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t xml:space="preserve">-59mm</t>
+          <t xml:space="preserve">-108mm</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Top</t>
+          <t xml:space="preserve">Bottom</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
